--- a/Wyniki/NOGI szablon.xlsx
+++ b/Wyniki/NOGI szablon.xlsx
@@ -498,15 +498,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Progresja: gdy ostatnia seria przekracza gorny pulap zakresu -&gt; nastepny trening dodaj 2,5 kg</t>
+          <t>Progresja: gdy ostatnia seria przekracza gorny pulap zakresu -&gt; nastepny trening dodaj 2,5 kg (izolacja: +1 kg)</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Przysiad ze sztanga</t>
+          <t>Przysiad ze sztanga [PIRAMIDA]</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -697,8 +697,10 @@
           <t>5-8</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>60</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>60 / 70 / 75 kg</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -711,25 +713,25 @@
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>RIR 3  –  5–6 powt., 3 w zapasie</t>
+          <t>RIR 3  –  5-6 powt., 3 w zapasie</t>
         </is>
       </c>
       <c r="J8" s="8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>RIR 2  –  6–7 powt., 2 w zapasie</t>
+          <t>RIR 2  –  6-7 powt., 2 w zapasie</t>
         </is>
       </c>
       <c r="M8" s="10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N8" s="10" t="n"/>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>RIR 1–2  –  7–8 powt., NIE do upadku!</t>
+          <t>RIR 1-2  –  7-8 powt., NIE do upadku!</t>
         </is>
       </c>
       <c r="P8" s="12" t="n"/>
@@ -741,7 +743,7 @@
       </c>
       <c r="T8" s="13" t="inlineStr">
         <is>
-          <t>stopy szerzej niz biodra, kolana nad stopami, pelny zakres</t>
+          <t>stopy szerzej niz biodra, kolana nad stopami, pelny zakres ruchu</t>
         </is>
       </c>
     </row>
@@ -751,7 +753,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bulgarian Split Squat</t>
+          <t>Bulgarian Split Squat [STALY]</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -791,7 +793,7 @@
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>RIR 1  –  9–10 powt., 1 w zapasie</t>
+          <t>RIR 1  –  9-10 powt., 1 w zapasie</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
@@ -814,7 +816,7 @@
       </c>
       <c r="T9" s="13" t="inlineStr">
         <is>
-          <t>tylna noga na lawce, biodra w dol, kolano nad stopa</t>
+          <t>tylna noga na lawce, biodra w dol, kolano nad stopa przodniej nogi</t>
         </is>
       </c>
     </row>
@@ -824,7 +826,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Hip Thrust ze sztanga</t>
+          <t>Hip Thrust ze sztanga [PIRAMIDA]</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -835,8 +837,10 @@
           <t>10-12</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>40</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>40 / 50 / 60 kg</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -853,16 +857,16 @@
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>RIR 1  –  11–12 powt., 1 w zapasie</t>
+          <t>RIR 1  –  11-12 powt., 1 w zapasie</t>
         </is>
       </c>
       <c r="M10" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N10" s="10" t="n"/>
       <c r="O10" s="11" t="inlineStr">
@@ -889,163 +893,235 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Copenhagen Plank (przywodziciele)</t>
+          <t>Leg Curl – uginanie nog [STALY]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10-15 sek</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BW</t>
+          <t>do ustalenia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NIE – izometria do wyznaczonego czasu</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>BW</t>
-        </is>
-      </c>
+          <t>TAK – ostatnia seria do upadku</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>trzymaj pozycje 10–15 sekund</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>BW</t>
-        </is>
-      </c>
+          <t>RIR 2  –  10 powt., 2 w zapasie</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="n"/>
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>trzymaj pozycje 10–15 sekund</t>
-        </is>
-      </c>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="12" t="n"/>
+          <t>RIR 1  –  11-12 powt., 1 w zapasie</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>RIR 0  –  DO UPADKU min 12</t>
+        </is>
+      </c>
       <c r="P11" s="12" t="n"/>
       <c r="Q11" s="12" t="n"/>
       <c r="R11" s="12" t="n"/>
       <c r="S11">
-        <f>IF(K11="","-",IF(ISNUMBER(K11),IF(K11&gt;15,"TAK – zwieksz czas","NIE – zostan z czasem"),"-"))</f>
+        <f>IF(N11="","-",IF(ISNUMBER(N11),IF(N11&gt;12,"TAK – dodaj 1 kg","NIE – zostan z ciezarem"),"-"))</f>
         <v/>
       </c>
       <c r="T11" s="13" t="inlineStr">
         <is>
+          <t>kontrolowane opuszczanie, pelny zakres – nie urywaj ruchu</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Odwodzenie na wyciagu jednorecz [STALY]</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>do ustalenia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TAK – ostatnia seria do upadku</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>RIR 2  –  12-13 powt., 2 w zapasie</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>RIR 1  –  13-14 powt., 1 w zapasie</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>RIR 0  –  DO UPADKU min 15</t>
+        </is>
+      </c>
+      <c r="P12" s="12" t="n"/>
+      <c r="Q12" s="12" t="n"/>
+      <c r="R12" s="12" t="n"/>
+      <c r="S12">
+        <f>IF(N12="","-",IF(ISNUMBER(N12),IF(N12&gt;15,"TAK – dodaj 1 kg","NIE – zostan z ciezarem"),"-"))</f>
+        <v/>
+      </c>
+      <c r="T12" s="13" t="inlineStr">
+        <is>
+          <t>lokiec lekko ugiety, kontrolowane opuszczanie, stabilne biodra</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Copenhagen Plank (przywodziciele)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10-15 sek</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NIE – izometria do wyznaczonego czasu</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>trzymaj pozycje 10-15 sekund</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>trzymaj pozycje 10-15 sekund</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="12" t="n"/>
+      <c r="R13" s="12" t="n"/>
+      <c r="S13">
+        <f>IF(K13="","-",IF(ISNUMBER(K13),IF(K13&gt;15,"TAK – zwieksz czas","NIE – zostan z czasem"),"-"))</f>
+        <v/>
+      </c>
+      <c r="T13" s="13" t="inlineStr">
+        <is>
           <t>gorna noga na lawce, dolna uniesiona – utrzymaj biodra w linii</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Kolory: zielony=RIR 3, niebieski=RIR 2, pomaranczowy=RIR 1, czerwony=RIR 0/upadek. Szare pola = seria nie w planie.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ROZGRZEWKA – NOGI</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Faza</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Cwiczenie / aktywnosc</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr"/>
-      <c r="D15" s="15" t="inlineStr"/>
-      <c r="E15" s="15" t="inlineStr"/>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Czas</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Wskazowka</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ogolna</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rower / orbitrek</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>umiarkowane tempo – podniesienie tetna i temperatury miesni</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Mobilnosc biodra</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Hip CARs – powolne krazenia (5 powt./strone)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>pelny zakres ruchu, kontrolowane – kluczowe dla squasha</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Przed przysiadem</t>
+          <t>Ogolna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goblet Squat z hantlem (lekkim) x 10 powt.</t>
+          <t>Rower / orbitrek</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1053,24 +1129,24 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>skupiasz sie na glebokosci i torze kolan</t>
+          <t>umiarkowane tempo – podniesienie tetna i temperatury miesni</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Przed przysiadem</t>
+          <t>Mobilnosc biodra</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gryf (20 kg) x 5 powt. – wolno</t>
+          <t>Hip CARs – powolne krazenia (5 powt./strone)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1078,31 +1154,81 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>czujesz ruch, sprawdzasz zakres</t>
+          <t>pelny zakres ruchu, kontrolowane – kluczowe dla squasha</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UWAGA</t>
+          <t>Przed przysiadem</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NIE rozciagaj statycznie przed treningiem – oslabienie sily!</t>
+          <t>Goblet Squat z hantlem (lekkim) x 10 powt.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>skupiasz sie na glebokosci i torze kolan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Przed przysiadem</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gryf (20 kg) x 5 powt. – wolno</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>czujesz ruch, sprawdzasz zakres</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UWAGA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NIE rozciagaj statycznie przed treningiem – oslabienie sily!</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1110,8 +1236,8 @@
     <mergeCell ref="A5:T5"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="G6:I6"/>
-    <mergeCell ref="A12:T12"/>
     <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A16:T16"/>
     <mergeCell ref="M6:O6"/>
     <mergeCell ref="P6:R6"/>
     <mergeCell ref="A14:T14"/>
